--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260811_203525.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260811_203525.xlsx
@@ -5754,7 +5754,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8656,7 +8656,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260811_203525.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260811_203525.xlsx
@@ -5754,7 +5754,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260811_203525.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260811_203525.xlsx
@@ -5754,7 +5754,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8656,7 +8656,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260811_203525.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260811_203525.xlsx
@@ -5754,7 +5754,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7052,7 +7052,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260811_203525.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260811_203525.xlsx
@@ -6826,7 +6826,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7052,7 +7052,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8656,7 +8656,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260811_203525.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260811_203525.xlsx
@@ -5754,7 +5754,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7052,7 +7052,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8656,7 +8656,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
